--- a/tests/resources/EVA_Submission_test_version_missing.xlsx
+++ b/tests/resources/EVA_Submission_test_version_missing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tcezard/PycharmProjects/eva-sub-cli/eva_sub_cli/etc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nkumar2/PycharmProjects/eva-sub-cli/tests/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A9AA12-83B5-5F4E-A99B-DAAE6E8CF182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLEASE READ FIRST" sheetId="1" r:id="rId1"/>
@@ -2356,7 +2356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2488,17 +2488,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2512,22 +2503,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2798,8 +2797,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1025" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="68"/>
-      <c r="B1" s="68"/>
+      <c r="A1" s="67"/>
+      <c r="B1" s="67"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -2808,10 +2807,10 @@
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:1025" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="71"/>
+      <c r="B2" s="68"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -2820,10 +2819,10 @@
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="69" t="s">
         <v>555</v>
       </c>
-      <c r="B3" s="72"/>
+      <c r="B3" s="69"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -2832,10 +2831,10 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="73"/>
+      <c r="B4" s="70"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2844,10 +2843,10 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:1025" s="5" customFormat="1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="74"/>
+      <c r="B5" s="71"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -3897,8 +3896,8 @@
       <c r="AMK7" s="5"/>
     </row>
     <row r="8" spans="1:1025" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="68"/>
-      <c r="B8" s="68"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="67"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -4924,10 +4923,10 @@
       <c r="AMK8" s="5"/>
     </row>
     <row r="9" spans="1:1025" ht="19" x14ac:dyDescent="0.25">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="69"/>
+      <c r="B9" s="73"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -5953,8 +5952,8 @@
       <c r="AMK9" s="5"/>
     </row>
     <row r="10" spans="1:1025" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="68"/>
-      <c r="B10" s="68"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="67"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -6980,10 +6979,10 @@
       <c r="AMK10" s="5"/>
     </row>
     <row r="11" spans="1:1025" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="70"/>
+      <c r="B11" s="74"/>
     </row>
     <row r="12" spans="1:1025" ht="20" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
@@ -7035,10 +7034,10 @@
       </c>
     </row>
     <row r="19" spans="1:1025" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="67"/>
+      <c r="B19" s="72"/>
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19"/>
@@ -8064,22 +8063,22 @@
       <c r="AMK19"/>
     </row>
     <row r="20" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="67"/>
+      <c r="B20" s="72"/>
     </row>
     <row r="21" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="67" t="s">
+      <c r="A21" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="67"/>
+      <c r="B21" s="72"/>
     </row>
     <row r="22" spans="1:1025" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="67"/>
+      <c r="B22" s="72"/>
     </row>
     <row r="23" spans="1:1025" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="19"/>
@@ -9111,11 +9110,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="pKFT46AcXRrznfWpmO12FPPtk8Stkq83/gBYtpLA8HQFC7aZLAdf2WJU+dOj9PZT/L7JPEe68/xM25EHPxktXQ==" saltValue="g+GUymTOlW49z+xbPyQ28w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="13">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
@@ -9124,6 +9118,11 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9686,7 +9685,7 @@
       <c r="B55" t="s">
         <v>317</v>
       </c>
-      <c r="E55" s="80" t="s">
+      <c r="E55" t="s">
         <v>551</v>
       </c>
     </row>
@@ -11950,10 +11949,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="77" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="79"/>
+      <c r="B1" s="77"/>
       <c r="C1" s="75"/>
       <c r="D1" s="43" t="s">
         <v>191</v>
@@ -12019,16 +12018,16 @@
       <c r="I2" s="78"/>
       <c r="J2" s="78"/>
       <c r="K2" s="78"/>
-      <c r="L2" s="77" t="s">
+      <c r="L2" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77" t="s">
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
       <c r="R2" s="78" t="s">
         <v>125</v>
       </c>
@@ -12220,16 +12219,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AI2"/>
+    <mergeCell ref="AJ2:AS2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="E1:E3"/>
     <mergeCell ref="F2:K2"/>
     <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:V2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AI2"/>
-    <mergeCell ref="AJ2:AS2"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Metadata and VCF" prompt="These sample names must match those provided in the VCF file(s)" sqref="E1 B4:B1003" xr:uid="{00000000-0002-0000-0700-000000000000}">
